--- a/reports/baseline_metrics.xlsx
+++ b/reports/baseline_metrics.xlsx
@@ -507,7 +507,7 @@
         <v>-0.4533532142479442</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008</v>
+        <v>0.0012</v>
       </c>
     </row>
   </sheetData>
